--- a/backend/storage/planwise_scenario_store.xlsx
+++ b/backend/storage/planwise_scenario_store.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712508</t>
+          <t>2026-07-23 16:51:17.419641</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -630,7 +630,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-07-21T21:08:39</t>
+          <t>2026-07-23T16:51:19</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y225"/>
+  <dimension ref="A1:AB225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,6 +930,21 @@
           <t>UpdatedDate</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>HeatingEndTime</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ReleaseTime</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>WaitingMinutes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1029,13 +1044,22 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712546</t>
+          <t>2026-07-23 16:51:17.419669</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712548</t>
-        </is>
+          <t>2026-07-23 16:51:17.419670</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1136,13 +1160,22 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712568</t>
+          <t>2026-07-23 16:51:17.419679</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712570</t>
-        </is>
+          <t>2026-07-23 16:51:17.419680</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1243,13 +1276,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712582</t>
+          <t>2026-07-23 16:51:17.419685</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712583</t>
-        </is>
+          <t>2026-07-23 16:51:17.419686</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1350,13 +1392,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712590</t>
+          <t>2026-07-23 16:51:17.419691</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712590</t>
-        </is>
+          <t>2026-07-23 16:51:17.419692</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1457,13 +1508,22 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712597</t>
+          <t>2026-07-23 16:51:17.419697</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712598</t>
-        </is>
+          <t>2026-07-23 16:51:17.419698</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1564,13 +1624,22 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712604</t>
+          <t>2026-07-23 16:51:17.419702</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712604</t>
-        </is>
+          <t>2026-07-23 16:51:17.419703</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1663,13 +1732,26 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712610</t>
+          <t>2026-07-23 16:51:17.419708</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712611</t>
-        </is>
+          <t>2026-07-23 16:51:17.419709</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:00:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1762,13 +1844,26 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712621</t>
+          <t>2026-07-23 16:51:17.419714</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712622</t>
-        </is>
+          <t>2026-07-23 16:51:17.419714</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1861,13 +1956,26 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712629</t>
+          <t>2026-07-23 16:51:17.419719</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712630</t>
-        </is>
+          <t>2026-07-23 16:51:17.419720</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:05:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1960,13 +2068,26 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712635</t>
+          <t>2026-07-23 16:51:17.419725</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712636</t>
-        </is>
+          <t>2026-07-23 16:51:17.419725</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:05:00</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -2059,13 +2180,26 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712641</t>
+          <t>2026-07-23 16:51:17.419730</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712642</t>
-        </is>
+          <t>2026-07-23 16:51:17.419731</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:10:00</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -2158,13 +2292,26 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712646</t>
+          <t>2026-07-23 16:51:17.419736</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712647</t>
-        </is>
+          <t>2026-07-23 16:51:17.419736</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-15 08:10:00</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -2265,13 +2412,22 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712652</t>
+          <t>2026-07-23 16:51:17.419742</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712653</t>
-        </is>
+          <t>2026-07-23 16:51:17.419742</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2372,13 +2528,22 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712657</t>
+          <t>2026-07-23 16:51:17.419747</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712658</t>
-        </is>
+          <t>2026-07-23 16:51:17.419748</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2479,13 +2644,22 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712662</t>
+          <t>2026-07-23 16:51:17.419752</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712663</t>
-        </is>
+          <t>2026-07-23 16:51:17.419753</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2586,13 +2760,22 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712668</t>
+          <t>2026-07-23 16:51:17.419758</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712669</t>
-        </is>
+          <t>2026-07-23 16:51:17.419758</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2693,13 +2876,22 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712673</t>
+          <t>2026-07-23 16:51:17.419763</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712674</t>
-        </is>
+          <t>2026-07-23 16:51:17.419764</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2800,13 +2992,22 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712678</t>
+          <t>2026-07-23 16:51:17.419769</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712679</t>
-        </is>
+          <t>2026-07-23 16:51:17.419769</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2899,13 +3100,26 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712683</t>
+          <t>2026-07-23 16:51:17.419775</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712684</t>
-        </is>
+          <t>2026-07-23 16:51:17.419775</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2998,13 +3212,26 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712688</t>
+          <t>2026-07-23 16:51:17.419780</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712689</t>
-        </is>
+          <t>2026-07-23 16:51:17.419781</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3097,13 +3324,26 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712698</t>
+          <t>2026-07-23 16:51:17.419785</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712699</t>
-        </is>
+          <t>2026-07-23 16:51:17.419786</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:20:00</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -3196,13 +3436,26 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712703</t>
+          <t>2026-07-23 16:51:17.419791</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712704</t>
-        </is>
+          <t>2026-07-23 16:51:17.419792</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:20:00</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -3295,13 +3548,26 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712709</t>
+          <t>2026-07-23 16:51:17.419796</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712709</t>
-        </is>
+          <t>2026-07-23 16:51:17.419797</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:25:00</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -3394,13 +3660,26 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712714</t>
+          <t>2026-07-23 16:51:17.419802</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712714</t>
-        </is>
+          <t>2026-07-23 16:51:17.419803</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:25:00</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -3501,13 +3780,22 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712719</t>
+          <t>2026-07-23 16:51:17.419807</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712720</t>
-        </is>
+          <t>2026-07-23 16:51:17.419808</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:30:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3608,13 +3896,22 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712724</t>
+          <t>2026-07-23 16:51:17.419813</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712725</t>
-        </is>
+          <t>2026-07-23 16:51:17.419813</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:30:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3715,13 +4012,22 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712730</t>
+          <t>2026-07-23 16:51:17.419818</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712731</t>
-        </is>
+          <t>2026-07-23 16:51:17.419819</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:30:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -3822,13 +4128,22 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712735</t>
+          <t>2026-07-23 16:51:17.419823</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712737</t>
-        </is>
+          <t>2026-07-23 16:51:17.419824</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:30:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3929,13 +4244,22 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712741</t>
+          <t>2026-07-23 16:51:17.419829</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712742</t>
-        </is>
+          <t>2026-07-23 16:51:17.419829</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:30:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -4036,13 +4360,22 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712747</t>
+          <t>2026-07-23 16:51:17.419834</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712747</t>
-        </is>
+          <t>2026-07-23 16:51:17.419835</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:30:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4135,13 +4468,26 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712752</t>
+          <t>2026-07-23 16:51:17.419839</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712753</t>
-        </is>
+          <t>2026-07-23 16:51:17.419840</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:30:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:30:00</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4234,13 +4580,26 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712757</t>
+          <t>2026-07-23 16:51:17.419845</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712758</t>
-        </is>
+          <t>2026-07-23 16:51:17.419845</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:30:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:30:00</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4333,13 +4692,26 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712762</t>
+          <t>2026-07-23 16:51:17.419850</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712763</t>
-        </is>
+          <t>2026-07-23 16:51:17.419851</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:30:00</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:35:00</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -4432,13 +4804,26 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712768</t>
+          <t>2026-07-23 16:51:17.419856</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712768</t>
-        </is>
+          <t>2026-07-23 16:51:17.419856</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:30:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:35:00</t>
+        </is>
+      </c>
+      <c r="AB35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -4531,13 +4916,26 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712773</t>
+          <t>2026-07-23 16:51:17.419861</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712774</t>
-        </is>
+          <t>2026-07-23 16:51:17.419862</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:30:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:40:00</t>
+        </is>
+      </c>
+      <c r="AB36" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -4630,13 +5028,26 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712778</t>
+          <t>2026-07-23 16:51:17.419866</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712779</t>
-        </is>
+          <t>2026-07-23 16:51:17.419867</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:30:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-15 12:40:00</t>
+        </is>
+      </c>
+      <c r="AB37" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -4737,13 +5148,22 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712784</t>
+          <t>2026-07-23 16:51:17.419872</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712784</t>
-        </is>
+          <t>2026-07-23 16:51:17.419873</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:00</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4844,13 +5264,22 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712792</t>
+          <t>2026-07-23 16:51:17.419877</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712793</t>
-        </is>
+          <t>2026-07-23 16:51:17.419878</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -4951,13 +5380,22 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712797</t>
+          <t>2026-07-23 16:51:17.419883</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712798</t>
-        </is>
+          <t>2026-07-23 16:51:17.419884</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:00</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -5058,13 +5496,22 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712803</t>
+          <t>2026-07-23 16:51:17.419888</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712803</t>
-        </is>
+          <t>2026-07-23 16:51:17.419889</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -5165,13 +5612,22 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712808</t>
+          <t>2026-07-23 16:51:17.419894</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712809</t>
-        </is>
+          <t>2026-07-23 16:51:17.419894</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -5272,13 +5728,22 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712813</t>
+          <t>2026-07-23 16:51:17.419899</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712814</t>
-        </is>
+          <t>2026-07-23 16:51:17.419900</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -5371,13 +5836,26 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712819</t>
+          <t>2026-07-23 16:51:17.419905</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712820</t>
-        </is>
+          <t>2026-07-23 16:51:17.419906</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:00</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:00</t>
+        </is>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -5470,13 +5948,26 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712824</t>
+          <t>2026-07-23 16:51:17.419910</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712825</t>
-        </is>
+          <t>2026-07-23 16:51:17.419911</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:00</t>
+        </is>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -5569,13 +6060,26 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712829</t>
+          <t>2026-07-23 16:51:17.419915</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712830</t>
-        </is>
+          <t>2026-07-23 16:51:17.419916</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:50:00</t>
+        </is>
+      </c>
+      <c r="AB46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -5668,13 +6172,26 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712835</t>
+          <t>2026-07-23 16:51:17.419921</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712835</t>
-        </is>
+          <t>2026-07-23 16:51:17.419922</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:00</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:50:00</t>
+        </is>
+      </c>
+      <c r="AB47" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -5767,13 +6284,26 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712840</t>
+          <t>2026-07-23 16:51:17.419927</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712841</t>
-        </is>
+          <t>2026-07-23 16:51:17.419928</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:00</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:55:00</t>
+        </is>
+      </c>
+      <c r="AB48" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="49">
@@ -5866,13 +6396,26 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712845</t>
+          <t>2026-07-23 16:51:17.419932</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712846</t>
-        </is>
+          <t>2026-07-23 16:51:17.419933</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:45:00</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-04-15 14:55:00</t>
+        </is>
+      </c>
+      <c r="AB49" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="50">
@@ -5973,13 +6516,22 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712852</t>
+          <t>2026-07-23 16:51:17.419938</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712852</t>
-        </is>
+          <t>2026-07-23 16:51:17.419939</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:00:00</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -6080,13 +6632,22 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712857</t>
+          <t>2026-07-23 16:51:17.419943</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712858</t>
-        </is>
+          <t>2026-07-23 16:51:17.419944</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:00:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -6187,13 +6748,22 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712862</t>
+          <t>2026-07-23 16:51:17.419949</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712863</t>
-        </is>
+          <t>2026-07-23 16:51:17.419950</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:00:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -6294,13 +6864,22 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712867</t>
+          <t>2026-07-23 16:51:17.419954</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712868</t>
-        </is>
+          <t>2026-07-23 16:51:17.419955</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:00:00</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -6401,13 +6980,22 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712873</t>
+          <t>2026-07-23 16:51:17.419959</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712873</t>
-        </is>
+          <t>2026-07-23 16:51:17.419960</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:00:00</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -6508,13 +7096,22 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712878</t>
+          <t>2026-07-23 16:51:17.419965</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712879</t>
-        </is>
+          <t>2026-07-23 16:51:17.419966</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:00:00</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -6607,13 +7204,26 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712886</t>
+          <t>2026-07-23 16:51:17.419970</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712887</t>
-        </is>
+          <t>2026-07-23 16:51:17.419971</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:00:00</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:00:00</t>
+        </is>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -6706,13 +7316,26 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712891</t>
+          <t>2026-07-23 16:51:17.419976</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712892</t>
-        </is>
+          <t>2026-07-23 16:51:17.419977</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:00:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:00:00</t>
+        </is>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -6805,13 +7428,26 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712897</t>
+          <t>2026-07-23 16:51:17.419981</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712898</t>
-        </is>
+          <t>2026-07-23 16:51:17.419982</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:00:00</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:05:00</t>
+        </is>
+      </c>
+      <c r="AB58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -6904,13 +7540,26 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712902</t>
+          <t>2026-07-23 16:51:17.419987</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712903</t>
-        </is>
+          <t>2026-07-23 16:51:17.419987</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:00:00</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:05:00</t>
+        </is>
+      </c>
+      <c r="AB59" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -7003,13 +7652,26 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712907</t>
+          <t>2026-07-23 16:51:17.419992</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712908</t>
-        </is>
+          <t>2026-07-23 16:51:17.419993</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:00:00</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:10:00</t>
+        </is>
+      </c>
+      <c r="AB60" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="61">
@@ -7102,13 +7764,26 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712913</t>
+          <t>2026-07-23 16:51:17.419997</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712914</t>
-        </is>
+          <t>2026-07-23 16:51:17.419998</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:00:00</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:10:00</t>
+        </is>
+      </c>
+      <c r="AB61" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="62">
@@ -7209,13 +7884,22 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712919</t>
+          <t>2026-07-23 16:51:17.420002</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712920</t>
-        </is>
+          <t>2026-07-23 16:51:17.420003</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:15:00</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -7316,13 +8000,22 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712924</t>
+          <t>2026-07-23 16:51:17.420008</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712925</t>
-        </is>
+          <t>2026-07-23 16:51:17.420008</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:15:00</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -7423,13 +8116,22 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712929</t>
+          <t>2026-07-23 16:51:17.420013</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712930</t>
-        </is>
+          <t>2026-07-23 16:51:17.420014</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:15:00</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -7530,13 +8232,22 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712934</t>
+          <t>2026-07-23 16:51:17.420018</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712935</t>
-        </is>
+          <t>2026-07-23 16:51:17.420019</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:15:00</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -7637,13 +8348,22 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712939</t>
+          <t>2026-07-23 16:51:17.420023</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712940</t>
-        </is>
+          <t>2026-07-23 16:51:17.420024</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:15:00</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -7744,13 +8464,22 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712945</t>
+          <t>2026-07-23 16:51:17.420029</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712946</t>
-        </is>
+          <t>2026-07-23 16:51:17.420030</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:15:00</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -7843,13 +8572,26 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712950</t>
+          <t>2026-07-23 16:51:17.420034</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712951</t>
-        </is>
+          <t>2026-07-23 16:51:17.420035</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:15:00</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:15:00</t>
+        </is>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -7942,13 +8684,26 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712956</t>
+          <t>2026-07-23 16:51:17.420040</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712956</t>
-        </is>
+          <t>2026-07-23 16:51:17.420041</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:15:00</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:15:00</t>
+        </is>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -8041,13 +8796,26 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712961</t>
+          <t>2026-07-23 16:51:17.420045</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712961</t>
-        </is>
+          <t>2026-07-23 16:51:17.420046</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:15:00</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:20:00</t>
+        </is>
+      </c>
+      <c r="AB70" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -8140,13 +8908,26 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712966</t>
+          <t>2026-07-23 16:51:17.420051</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712966</t>
-        </is>
+          <t>2026-07-23 16:51:17.420051</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:15:00</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:20:00</t>
+        </is>
+      </c>
+      <c r="AB71" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -8239,13 +9020,26 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712971</t>
+          <t>2026-07-23 16:51:17.420056</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712971</t>
-        </is>
+          <t>2026-07-23 16:51:17.420057</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:15:00</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:25:00</t>
+        </is>
+      </c>
+      <c r="AB72" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="73">
@@ -8338,13 +9132,26 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712976</t>
+          <t>2026-07-23 16:51:17.420061</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712976</t>
-        </is>
+          <t>2026-07-23 16:51:17.420062</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:15:00</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-04-15 19:25:00</t>
+        </is>
+      </c>
+      <c r="AB73" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -8445,13 +9252,22 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712981</t>
+          <t>2026-07-23 16:51:17.420067</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712982</t>
-        </is>
+          <t>2026-07-23 16:51:17.420067</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -8552,13 +9368,22 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712986</t>
+          <t>2026-07-23 16:51:17.420072</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712987</t>
-        </is>
+          <t>2026-07-23 16:51:17.420073</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -8659,13 +9484,22 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712991</t>
+          <t>2026-07-23 16:51:17.420077</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712992</t>
-        </is>
+          <t>2026-07-23 16:51:17.420078</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -8766,13 +9600,22 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712997</t>
+          <t>2026-07-23 16:51:17.420082</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.712997</t>
-        </is>
+          <t>2026-07-23 16:51:17.420083</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -8873,13 +9716,22 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713002</t>
+          <t>2026-07-23 16:51:17.420088</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713003</t>
-        </is>
+          <t>2026-07-23 16:51:17.420088</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -8980,13 +9832,22 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713008</t>
+          <t>2026-07-23 16:51:17.420094</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713009</t>
-        </is>
+          <t>2026-07-23 16:51:17.420095</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -9079,13 +9940,26 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713013</t>
+          <t>2026-07-23 16:51:17.420100</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713014</t>
-        </is>
+          <t>2026-07-23 16:51:17.420100</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -9178,13 +10052,26 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713018</t>
+          <t>2026-07-23 16:51:17.420105</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713019</t>
-        </is>
+          <t>2026-07-23 16:51:17.420106</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="AB81" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -9277,13 +10164,26 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713023</t>
+          <t>2026-07-23 16:51:17.420110</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713024</t>
-        </is>
+          <t>2026-07-23 16:51:17.420111</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:35:00</t>
+        </is>
+      </c>
+      <c r="AB82" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -9376,13 +10276,26 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713028</t>
+          <t>2026-07-23 16:51:17.420116</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713029</t>
-        </is>
+          <t>2026-07-23 16:51:17.420117</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:35:00</t>
+        </is>
+      </c>
+      <c r="AB83" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -9475,13 +10388,26 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713033</t>
+          <t>2026-07-23 16:51:17.420121</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713034</t>
-        </is>
+          <t>2026-07-23 16:51:17.420122</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:40:00</t>
+        </is>
+      </c>
+      <c r="AB84" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="85">
@@ -9574,13 +10500,26 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713038</t>
+          <t>2026-07-23 16:51:17.420126</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713039</t>
-        </is>
+          <t>2026-07-23 16:51:17.420127</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:30:00</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-04-15 21:40:00</t>
+        </is>
+      </c>
+      <c r="AB85" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="86">
@@ -9681,13 +10620,22 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713043</t>
+          <t>2026-07-23 16:51:17.420132</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713044</t>
-        </is>
+          <t>2026-07-23 16:51:17.420133</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:45:00</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -9788,13 +10736,22 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713048</t>
+          <t>2026-07-23 16:51:17.420138</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713049</t>
-        </is>
+          <t>2026-07-23 16:51:17.420139</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:45:00</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -9895,13 +10852,22 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713053</t>
+          <t>2026-07-23 16:51:17.420143</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713054</t>
-        </is>
+          <t>2026-07-23 16:51:17.420144</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:45:00</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -10002,13 +10968,22 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713058</t>
+          <t>2026-07-23 16:51:17.420148</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713059</t>
-        </is>
+          <t>2026-07-23 16:51:17.420149</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:45:00</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -10109,13 +11084,22 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713063</t>
+          <t>2026-07-23 16:51:17.420154</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713064</t>
-        </is>
+          <t>2026-07-23 16:51:17.420155</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:45:00</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -10216,13 +11200,22 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713068</t>
+          <t>2026-07-23 16:51:17.420159</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713069</t>
-        </is>
+          <t>2026-07-23 16:51:17.420160</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:45:00</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -10315,13 +11308,26 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713073</t>
+          <t>2026-07-23 16:51:17.420165</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713074</t>
-        </is>
+          <t>2026-07-23 16:51:17.420166</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:45:00</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:45:00</t>
+        </is>
+      </c>
+      <c r="AB92" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -10414,13 +11420,26 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713078</t>
+          <t>2026-07-23 16:51:17.420170</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713079</t>
-        </is>
+          <t>2026-07-23 16:51:17.420171</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:45:00</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:45:00</t>
+        </is>
+      </c>
+      <c r="AB93" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -10513,13 +11532,26 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713083</t>
+          <t>2026-07-23 16:51:17.420176</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713084</t>
-        </is>
+          <t>2026-07-23 16:51:17.420176</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:45:00</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:50:00</t>
+        </is>
+      </c>
+      <c r="AB94" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -10612,13 +11644,26 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713089</t>
+          <t>2026-07-23 16:51:17.420181</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713090</t>
-        </is>
+          <t>2026-07-23 16:51:17.420182</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:45:00</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:50:00</t>
+        </is>
+      </c>
+      <c r="AB95" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="96">
@@ -10711,13 +11756,26 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713094</t>
+          <t>2026-07-23 16:51:17.420187</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713095</t>
-        </is>
+          <t>2026-07-23 16:51:17.420187</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:45:00</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:55:00</t>
+        </is>
+      </c>
+      <c r="AB96" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="97">
@@ -10810,13 +11868,26 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713099</t>
+          <t>2026-07-23 16:51:17.420192</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713100</t>
-        </is>
+          <t>2026-07-23 16:51:17.420193</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:45:00</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-04-15 23:55:00</t>
+        </is>
+      </c>
+      <c r="AB97" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="98">
@@ -10917,13 +11988,22 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713105</t>
+          <t>2026-07-23 16:51:17.420197</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713105</t>
-        </is>
+          <t>2026-07-23 16:51:17.420198</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>2026-04-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -11024,13 +12104,22 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713110</t>
+          <t>2026-07-23 16:51:17.420203</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713110</t>
-        </is>
+          <t>2026-07-23 16:51:17.420204</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>2026-04-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -11131,13 +12220,22 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713115</t>
+          <t>2026-07-23 16:51:17.420208</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713115</t>
-        </is>
+          <t>2026-07-23 16:51:17.420209</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>2026-04-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -11230,13 +12328,26 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713120</t>
+          <t>2026-07-23 16:51:17.420214</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713120</t>
-        </is>
+          <t>2026-07-23 16:51:17.420214</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>2026-04-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-04-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="AB101" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -11329,13 +12440,26 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713125</t>
+          <t>2026-07-23 16:51:17.420219</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713125</t>
-        </is>
+          <t>2026-07-23 16:51:17.420220</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>2026-04-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-04-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="AB102" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -11428,13 +12552,26 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713130</t>
+          <t>2026-07-23 16:51:17.420225</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713130</t>
-        </is>
+          <t>2026-07-23 16:51:17.420225</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>2026-04-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-04-16 00:05:00</t>
+        </is>
+      </c>
+      <c r="AB103" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="104">
@@ -11535,13 +12672,22 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713135</t>
+          <t>2026-07-23 16:51:17.420230</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713135</t>
-        </is>
+          <t>2026-07-23 16:51:17.420231</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>2026-04-16 02:10:00</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -11642,13 +12788,22 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713140</t>
+          <t>2026-07-23 16:51:17.420235</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713140</t>
-        </is>
+          <t>2026-07-23 16:51:17.420236</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>2026-04-16 02:10:00</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -11749,13 +12904,22 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713145</t>
+          <t>2026-07-23 16:51:17.420241</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713146</t>
-        </is>
+          <t>2026-07-23 16:51:17.420241</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>2026-04-16 02:10:00</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -11848,13 +13012,26 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713150</t>
+          <t>2026-07-23 16:51:17.420246</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713151</t>
-        </is>
+          <t>2026-07-23 16:51:17.420247</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>2026-04-16 02:10:00</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-04-16 02:10:00</t>
+        </is>
+      </c>
+      <c r="AB107" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -11947,13 +13124,26 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713155</t>
+          <t>2026-07-23 16:51:17.420252</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713156</t>
-        </is>
+          <t>2026-07-23 16:51:17.420252</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>2026-04-16 02:10:00</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-04-16 02:10:00</t>
+        </is>
+      </c>
+      <c r="AB108" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -12046,13 +13236,26 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713160</t>
+          <t>2026-07-23 16:51:17.420257</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713161</t>
-        </is>
+          <t>2026-07-23 16:51:17.420258</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>2026-04-16 02:10:00</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-04-16 02:15:00</t>
+        </is>
+      </c>
+      <c r="AB109" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="110">
@@ -12153,13 +13356,22 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713165</t>
+          <t>2026-07-23 16:51:17.420263</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713165</t>
-        </is>
+          <t>2026-07-23 16:51:17.420263</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>2026-04-16 04:20:00</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -12260,13 +13472,22 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713171</t>
+          <t>2026-07-23 16:51:17.420269</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713171</t>
-        </is>
+          <t>2026-07-23 16:51:17.420270</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>2026-04-16 04:20:00</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr"/>
+      <c r="AB111" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -12367,13 +13588,22 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713176</t>
+          <t>2026-07-23 16:51:17.420275</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713176</t>
-        </is>
+          <t>2026-07-23 16:51:17.420275</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>2026-04-16 04:20:00</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -12466,13 +13696,26 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713181</t>
+          <t>2026-07-23 16:51:17.420280</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713181</t>
-        </is>
+          <t>2026-07-23 16:51:17.420281</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>2026-04-16 04:20:00</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-04-16 04:20:00</t>
+        </is>
+      </c>
+      <c r="AB113" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -12565,13 +13808,26 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713186</t>
+          <t>2026-07-23 16:51:17.420286</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713186</t>
-        </is>
+          <t>2026-07-23 16:51:17.420286</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>2026-04-16 04:20:00</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-04-16 04:20:00</t>
+        </is>
+      </c>
+      <c r="AB114" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -12664,13 +13920,26 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713191</t>
+          <t>2026-07-23 16:51:17.420291</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713191</t>
-        </is>
+          <t>2026-07-23 16:51:17.420292</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>2026-04-16 04:20:00</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2026-04-16 04:25:00</t>
+        </is>
+      </c>
+      <c r="AB115" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="116">
@@ -12771,13 +14040,22 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713196</t>
+          <t>2026-07-23 16:51:17.420296</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713196</t>
-        </is>
+          <t>2026-07-23 16:51:17.420297</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>2026-04-16 06:30:00</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -12878,13 +14156,22 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713201</t>
+          <t>2026-07-23 16:51:17.420302</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713201</t>
-        </is>
+          <t>2026-07-23 16:51:17.420303</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>2026-04-16 06:30:00</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -12985,13 +14272,22 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713206</t>
+          <t>2026-07-23 16:51:17.420307</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713207</t>
-        </is>
+          <t>2026-07-23 16:51:17.420308</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>2026-04-16 06:30:00</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr"/>
+      <c r="AB118" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -13084,13 +14380,26 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713211</t>
+          <t>2026-07-23 16:51:17.420313</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713211</t>
-        </is>
+          <t>2026-07-23 16:51:17.420313</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>2026-04-16 06:30:00</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2026-04-16 06:30:00</t>
+        </is>
+      </c>
+      <c r="AB119" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -13183,13 +14492,26 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713216</t>
+          <t>2026-07-23 16:51:17.420318</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713216</t>
-        </is>
+          <t>2026-07-23 16:51:17.420319</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>2026-04-16 06:30:00</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-04-16 06:30:00</t>
+        </is>
+      </c>
+      <c r="AB120" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -13282,13 +14604,26 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713221</t>
+          <t>2026-07-23 16:51:17.420324</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713221</t>
-        </is>
+          <t>2026-07-23 16:51:17.420325</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>2026-04-16 06:30:00</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2026-04-16 06:35:00</t>
+        </is>
+      </c>
+      <c r="AB121" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="122">
@@ -13389,13 +14724,22 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713226</t>
+          <t>2026-07-23 16:51:17.420329</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713226</t>
-        </is>
+          <t>2026-07-23 16:51:17.420330</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:40:00</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr"/>
+      <c r="AB122" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -13496,13 +14840,22 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713231</t>
+          <t>2026-07-23 16:51:17.420335</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713232</t>
-        </is>
+          <t>2026-07-23 16:51:17.420336</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:40:00</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr"/>
+      <c r="AB123" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -13603,13 +14956,22 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713236</t>
+          <t>2026-07-23 16:51:17.420340</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713237</t>
-        </is>
+          <t>2026-07-23 16:51:17.420341</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:40:00</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -13702,13 +15064,26 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713241</t>
+          <t>2026-07-23 16:51:17.420345</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713242</t>
-        </is>
+          <t>2026-07-23 16:51:17.420346</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:40:00</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:40:00</t>
+        </is>
+      </c>
+      <c r="AB125" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -13801,13 +15176,26 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713246</t>
+          <t>2026-07-23 16:51:17.420351</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713246</t>
-        </is>
+          <t>2026-07-23 16:51:17.420352</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:40:00</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:40:00</t>
+        </is>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -13900,13 +15288,26 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713251</t>
+          <t>2026-07-23 16:51:17.420356</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713251</t>
-        </is>
+          <t>2026-07-23 16:51:17.420357</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:40:00</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:45:00</t>
+        </is>
+      </c>
+      <c r="AB127" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="128">
@@ -14007,13 +15408,22 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713256</t>
+          <t>2026-07-23 16:51:17.420362</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713256</t>
-        </is>
+          <t>2026-07-23 16:51:17.420363</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:50:00</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr"/>
+      <c r="AB128" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -14114,13 +15524,22 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713261</t>
+          <t>2026-07-23 16:51:17.420367</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713262</t>
-        </is>
+          <t>2026-07-23 16:51:17.420368</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:50:00</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -14221,13 +15640,22 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713266</t>
+          <t>2026-07-23 16:51:17.420373</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713267</t>
-        </is>
+          <t>2026-07-23 16:51:17.420374</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:50:00</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -14320,13 +15748,26 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713272</t>
+          <t>2026-07-23 16:51:17.420379</t>
         </is>
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713272</t>
-        </is>
+          <t>2026-07-23 16:51:17.420380</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:50:00</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:50:00</t>
+        </is>
+      </c>
+      <c r="AB131" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -14419,13 +15860,26 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713277</t>
+          <t>2026-07-23 16:51:17.420385</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713278</t>
-        </is>
+          <t>2026-07-23 16:51:17.420386</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:50:00</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:50:00</t>
+        </is>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -14518,13 +15972,26 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713282</t>
+          <t>2026-07-23 16:51:17.420390</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713283</t>
-        </is>
+          <t>2026-07-23 16:51:17.420391</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:50:00</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:55:00</t>
+        </is>
+      </c>
+      <c r="AB133" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="134">
@@ -14625,13 +16092,22 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713287</t>
+          <t>2026-07-23 16:51:17.420396</t>
         </is>
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713288</t>
-        </is>
+          <t>2026-07-23 16:51:17.420397</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:00:00</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -14732,13 +16208,22 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713292</t>
+          <t>2026-07-23 16:51:17.420401</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713293</t>
-        </is>
+          <t>2026-07-23 16:51:17.420402</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:00:00</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -14839,13 +16324,22 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713297</t>
+          <t>2026-07-23 16:51:17.420406</t>
         </is>
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713298</t>
-        </is>
+          <t>2026-07-23 16:51:17.420407</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:00:00</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr"/>
+      <c r="AB136" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -14938,13 +16432,26 @@
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713302</t>
+          <t>2026-07-23 16:51:17.420412</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713303</t>
-        </is>
+          <t>2026-07-23 16:51:17.420413</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:00:00</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:00:00</t>
+        </is>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -15037,13 +16544,26 @@
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713307</t>
+          <t>2026-07-23 16:51:17.420417</t>
         </is>
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713307</t>
-        </is>
+          <t>2026-07-23 16:51:17.420418</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:00:00</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:00:00</t>
+        </is>
+      </c>
+      <c r="AB138" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -15136,13 +16656,26 @@
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713312</t>
+          <t>2026-07-23 16:51:17.420423</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713313</t>
-        </is>
+          <t>2026-07-23 16:51:17.420423</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:00:00</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:05:00</t>
+        </is>
+      </c>
+      <c r="AB139" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="140">
@@ -15243,13 +16776,22 @@
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713317</t>
+          <t>2026-07-23 16:51:17.420428</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713318</t>
-        </is>
+          <t>2026-07-23 16:51:17.420429</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:10:00</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr"/>
+      <c r="AB140" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -15350,13 +16892,22 @@
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713322</t>
+          <t>2026-07-23 16:51:17.420434</t>
         </is>
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713323</t>
-        </is>
+          <t>2026-07-23 16:51:17.420435</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:10:00</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr"/>
+      <c r="AB141" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -15457,13 +17008,22 @@
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713328</t>
+          <t>2026-07-23 16:51:17.420439</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713329</t>
-        </is>
+          <t>2026-07-23 16:51:17.420440</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:10:00</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -15556,13 +17116,26 @@
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713333</t>
+          <t>2026-07-23 16:51:17.420444</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713334</t>
-        </is>
+          <t>2026-07-23 16:51:17.420445</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:10:00</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:10:00</t>
+        </is>
+      </c>
+      <c r="AB143" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -15655,13 +17228,26 @@
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713338</t>
+          <t>2026-07-23 16:51:17.420450</t>
         </is>
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713339</t>
-        </is>
+          <t>2026-07-23 16:51:17.420451</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:10:00</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:10:00</t>
+        </is>
+      </c>
+      <c r="AB144" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -15754,13 +17340,26 @@
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713343</t>
+          <t>2026-07-23 16:51:17.420455</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713344</t>
-        </is>
+          <t>2026-07-23 16:51:17.420456</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:10:00</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:15:00</t>
+        </is>
+      </c>
+      <c r="AB145" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="146">
@@ -15861,13 +17460,22 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713349</t>
+          <t>2026-07-23 16:51:17.420461</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713350</t>
-        </is>
+          <t>2026-07-23 16:51:17.420462</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>2026-04-17 01:30:00</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr"/>
+      <c r="AB146" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -15968,13 +17576,22 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713354</t>
+          <t>2026-07-23 16:51:17.420466</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713355</t>
-        </is>
+          <t>2026-07-23 16:51:17.420467</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>2026-04-17 01:30:00</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -16075,13 +17692,22 @@
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713359</t>
+          <t>2026-07-23 16:51:17.420472</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713360</t>
-        </is>
+          <t>2026-07-23 16:51:17.420473</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>2026-04-17 01:30:00</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr"/>
+      <c r="AB148" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -16174,13 +17800,26 @@
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713364</t>
+          <t>2026-07-23 16:51:17.420477</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713365</t>
-        </is>
+          <t>2026-07-23 16:51:17.420478</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>2026-04-17 01:30:00</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2026-04-17 01:30:00</t>
+        </is>
+      </c>
+      <c r="AB149" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -16273,13 +17912,26 @@
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713369</t>
+          <t>2026-07-23 16:51:17.420483</t>
         </is>
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713370</t>
-        </is>
+          <t>2026-07-23 16:51:17.420483</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>2026-04-17 01:30:00</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2026-04-17 01:35:00</t>
+        </is>
+      </c>
+      <c r="AB150" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="151">
@@ -16372,13 +18024,26 @@
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713374</t>
+          <t>2026-07-23 16:51:17.420488</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713375</t>
-        </is>
+          <t>2026-07-23 16:51:17.420489</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>2026-04-17 01:30:00</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2026-04-17 01:35:00</t>
+        </is>
+      </c>
+      <c r="AB151" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="152">
@@ -16479,13 +18144,22 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713380</t>
+          <t>2026-07-23 16:51:17.420494</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713381</t>
-        </is>
+          <t>2026-07-23 16:51:17.420494</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:40:00</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr"/>
+      <c r="AB152" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -16586,13 +18260,22 @@
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713385</t>
+          <t>2026-07-23 16:51:17.420499</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713386</t>
-        </is>
+          <t>2026-07-23 16:51:17.420500</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:40:00</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr"/>
+      <c r="AB153" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -16693,13 +18376,22 @@
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713390</t>
+          <t>2026-07-23 16:51:17.420504</t>
         </is>
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713391</t>
-        </is>
+          <t>2026-07-23 16:51:17.420505</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:40:00</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr"/>
+      <c r="AB154" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -16792,13 +18484,26 @@
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713395</t>
+          <t>2026-07-23 16:51:17.420510</t>
         </is>
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713396</t>
-        </is>
+          <t>2026-07-23 16:51:17.420511</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:40:00</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:40:00</t>
+        </is>
+      </c>
+      <c r="AB155" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -16891,13 +18596,26 @@
       </c>
       <c r="X156" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713400</t>
+          <t>2026-07-23 16:51:17.420515</t>
         </is>
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713401</t>
-        </is>
+          <t>2026-07-23 16:51:17.420516</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:40:00</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:40:00</t>
+        </is>
+      </c>
+      <c r="AB156" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -16990,13 +18708,26 @@
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713405</t>
+          <t>2026-07-23 16:51:17.420521</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713406</t>
-        </is>
+          <t>2026-07-23 16:51:17.420521</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:40:00</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:45:00</t>
+        </is>
+      </c>
+      <c r="AB157" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="158">
@@ -17097,13 +18828,22 @@
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713410</t>
+          <t>2026-07-23 16:51:17.420526</t>
         </is>
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713411</t>
-        </is>
+          <t>2026-07-23 16:51:17.420527</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>2026-04-17 05:50:00</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr"/>
+      <c r="AB158" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -17204,13 +18944,22 @@
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713415</t>
+          <t>2026-07-23 16:51:17.420531</t>
         </is>
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713416</t>
-        </is>
+          <t>2026-07-23 16:51:17.420532</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>2026-04-17 05:50:00</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr"/>
+      <c r="AB159" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -17311,13 +19060,22 @@
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713420</t>
+          <t>2026-07-23 16:51:17.420537</t>
         </is>
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713420</t>
-        </is>
+          <t>2026-07-23 16:51:17.420538</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>2026-04-17 05:50:00</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr"/>
+      <c r="AB160" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -17410,13 +19168,26 @@
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713425</t>
+          <t>2026-07-23 16:51:17.420542</t>
         </is>
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713425</t>
-        </is>
+          <t>2026-07-23 16:51:17.420543</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>2026-04-17 05:50:00</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2026-04-17 05:50:00</t>
+        </is>
+      </c>
+      <c r="AB161" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -17509,13 +19280,26 @@
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713430</t>
+          <t>2026-07-23 16:51:17.420548</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713430</t>
-        </is>
+          <t>2026-07-23 16:51:17.420548</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>2026-04-17 05:50:00</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2026-04-17 05:50:00</t>
+        </is>
+      </c>
+      <c r="AB162" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -17608,13 +19392,26 @@
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713435</t>
+          <t>2026-07-23 16:51:17.420553</t>
         </is>
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713435</t>
-        </is>
+          <t>2026-07-23 16:51:17.420554</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>2026-04-17 05:50:00</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2026-04-17 05:55:00</t>
+        </is>
+      </c>
+      <c r="AB163" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="164">
@@ -17715,13 +19512,22 @@
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713440</t>
+          <t>2026-07-23 16:51:17.420558</t>
         </is>
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713440</t>
-        </is>
+          <t>2026-07-23 16:51:17.420559</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr"/>
+      <c r="AB164" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -17822,13 +19628,22 @@
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713445</t>
+          <t>2026-07-23 16:51:17.420564</t>
         </is>
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713446</t>
-        </is>
+          <t>2026-07-23 16:51:17.420564</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr"/>
+      <c r="AB165" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -17929,13 +19744,22 @@
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713450</t>
+          <t>2026-07-23 16:51:17.420569</t>
         </is>
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713451</t>
-        </is>
+          <t>2026-07-23 16:51:17.420570</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr"/>
+      <c r="AB166" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -18028,13 +19852,26 @@
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713456</t>
+          <t>2026-07-23 16:51:17.420574</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713456</t>
-        </is>
+          <t>2026-07-23 16:51:17.420575</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:00:00</t>
+        </is>
+      </c>
+      <c r="AB167" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -18127,13 +19964,26 @@
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713461</t>
+          <t>2026-07-23 16:51:17.420579</t>
         </is>
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713461</t>
-        </is>
+          <t>2026-07-23 16:51:17.420580</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:00:00</t>
+        </is>
+      </c>
+      <c r="AB168" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -18226,13 +20076,26 @@
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713466</t>
+          <t>2026-07-23 16:51:17.420585</t>
         </is>
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713467</t>
-        </is>
+          <t>2026-07-23 16:51:17.420585</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:00:00</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:05:00</t>
+        </is>
+      </c>
+      <c r="AB169" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="170">
@@ -18333,13 +20196,22 @@
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713471</t>
+          <t>2026-07-23 16:51:17.420590</t>
         </is>
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713472</t>
-        </is>
+          <t>2026-07-23 16:51:17.420591</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:10:00</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr"/>
+      <c r="AB170" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -18440,13 +20312,22 @@
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713476</t>
+          <t>2026-07-23 16:51:17.420595</t>
         </is>
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713477</t>
-        </is>
+          <t>2026-07-23 16:51:17.420596</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:10:00</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr"/>
+      <c r="AB171" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -18547,13 +20428,22 @@
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713481</t>
+          <t>2026-07-23 16:51:17.420601</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713482</t>
-        </is>
+          <t>2026-07-23 16:51:17.420602</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:10:00</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr"/>
+      <c r="AB172" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -18646,13 +20536,26 @@
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713486</t>
+          <t>2026-07-23 16:51:17.420606</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713487</t>
-        </is>
+          <t>2026-07-23 16:51:17.420607</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:10:00</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:10:00</t>
+        </is>
+      </c>
+      <c r="AB173" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -18745,13 +20648,26 @@
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713492</t>
+          <t>2026-07-23 16:51:17.420612</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713493</t>
-        </is>
+          <t>2026-07-23 16:51:17.420612</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:10:00</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:10:00</t>
+        </is>
+      </c>
+      <c r="AB174" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -18844,13 +20760,26 @@
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713497</t>
+          <t>2026-07-23 16:51:17.420617</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713498</t>
-        </is>
+          <t>2026-07-23 16:51:17.420618</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:10:00</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:15:00</t>
+        </is>
+      </c>
+      <c r="AB175" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="176">
@@ -18951,13 +20880,22 @@
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713502</t>
+          <t>2026-07-23 16:51:17.420623</t>
         </is>
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713503</t>
-        </is>
+          <t>2026-07-23 16:51:17.420624</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:20:00</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr"/>
+      <c r="AB176" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -19058,13 +20996,22 @@
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713508</t>
+          <t>2026-07-23 16:51:17.420629</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713508</t>
-        </is>
+          <t>2026-07-23 16:51:17.420629</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:20:00</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr"/>
+      <c r="AB177" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -19165,13 +21112,22 @@
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713513</t>
+          <t>2026-07-23 16:51:17.420634</t>
         </is>
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713514</t>
-        </is>
+          <t>2026-07-23 16:51:17.420635</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:20:00</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr"/>
+      <c r="AB178" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -19264,13 +21220,26 @@
       </c>
       <c r="X179" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713518</t>
+          <t>2026-07-23 16:51:17.420640</t>
         </is>
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713519</t>
-        </is>
+          <t>2026-07-23 16:51:17.420640</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:20:00</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:20:00</t>
+        </is>
+      </c>
+      <c r="AB179" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -19363,13 +21332,26 @@
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713523</t>
+          <t>2026-07-23 16:51:17.420645</t>
         </is>
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713524</t>
-        </is>
+          <t>2026-07-23 16:51:17.420646</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:20:00</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:20:00</t>
+        </is>
+      </c>
+      <c r="AB180" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -19462,13 +21444,26 @@
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713528</t>
+          <t>2026-07-23 16:51:17.420651</t>
         </is>
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713529</t>
-        </is>
+          <t>2026-07-23 16:51:17.420651</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:20:00</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:25:00</t>
+        </is>
+      </c>
+      <c r="AB181" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="182">
@@ -19569,13 +21564,22 @@
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713534</t>
+          <t>2026-07-23 16:51:17.420656</t>
         </is>
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713534</t>
-        </is>
+          <t>2026-07-23 16:51:17.420657</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>2026-04-17 14:30:00</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr"/>
+      <c r="AB182" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -19676,13 +21680,22 @@
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713539</t>
+          <t>2026-07-23 16:51:17.420661</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713540</t>
-        </is>
+          <t>2026-07-23 16:51:17.420662</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>2026-04-17 14:30:00</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr"/>
+      <c r="AB183" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -19783,13 +21796,22 @@
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713544</t>
+          <t>2026-07-23 16:51:17.420666</t>
         </is>
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713545</t>
-        </is>
+          <t>2026-07-23 16:51:17.420667</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>2026-04-17 14:30:00</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr"/>
+      <c r="AB184" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -19882,13 +21904,26 @@
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713549</t>
+          <t>2026-07-23 16:51:17.420672</t>
         </is>
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713550</t>
-        </is>
+          <t>2026-07-23 16:51:17.420673</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>2026-04-17 14:30:00</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2026-04-17 14:30:00</t>
+        </is>
+      </c>
+      <c r="AB185" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -19981,13 +22016,26 @@
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713554</t>
+          <t>2026-07-23 16:51:17.420677</t>
         </is>
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713555</t>
-        </is>
+          <t>2026-07-23 16:51:17.420678</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>2026-04-17 14:30:00</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2026-04-17 14:30:00</t>
+        </is>
+      </c>
+      <c r="AB186" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -20080,13 +22128,26 @@
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713559</t>
+          <t>2026-07-23 16:51:17.420683</t>
         </is>
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713560</t>
-        </is>
+          <t>2026-07-23 16:51:17.420684</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>2026-04-17 14:30:00</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2026-04-17 14:35:00</t>
+        </is>
+      </c>
+      <c r="AB187" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="188">
@@ -20187,13 +22248,22 @@
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713564</t>
+          <t>2026-07-23 16:51:17.420689</t>
         </is>
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713565</t>
-        </is>
+          <t>2026-07-23 16:51:17.420689</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:40:00</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr"/>
+      <c r="AB188" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -20294,13 +22364,22 @@
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713569</t>
+          <t>2026-07-23 16:51:17.420694</t>
         </is>
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713570</t>
-        </is>
+          <t>2026-07-23 16:51:17.420695</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:40:00</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr"/>
+      <c r="AB189" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -20401,13 +22480,22 @@
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713575</t>
+          <t>2026-07-23 16:51:17.420700</t>
         </is>
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713575</t>
-        </is>
+          <t>2026-07-23 16:51:17.420701</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:40:00</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr"/>
+      <c r="AB190" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -20500,13 +22588,26 @@
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713580</t>
+          <t>2026-07-23 16:51:17.420705</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713580</t>
-        </is>
+          <t>2026-07-23 16:51:17.420706</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:40:00</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:40:00</t>
+        </is>
+      </c>
+      <c r="AB191" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -20599,13 +22700,26 @@
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713585</t>
+          <t>2026-07-23 16:51:17.420711</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713586</t>
-        </is>
+          <t>2026-07-23 16:51:17.420712</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:40:00</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:40:00</t>
+        </is>
+      </c>
+      <c r="AB192" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -20698,13 +22812,26 @@
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713590</t>
+          <t>2026-07-23 16:51:17.420717</t>
         </is>
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713591</t>
-        </is>
+          <t>2026-07-23 16:51:17.420717</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:40:00</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:45:00</t>
+        </is>
+      </c>
+      <c r="AB193" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="194">
@@ -20805,13 +22932,22 @@
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713595</t>
+          <t>2026-07-23 16:51:17.420722</t>
         </is>
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713596</t>
-        </is>
+          <t>2026-07-23 16:51:17.420723</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:45:00</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr"/>
+      <c r="AB194" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -20912,13 +23048,22 @@
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713600</t>
+          <t>2026-07-23 16:51:17.420728</t>
         </is>
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713601</t>
-        </is>
+          <t>2026-07-23 16:51:17.420729</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:45:00</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr"/>
+      <c r="AB195" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -21011,13 +23156,26 @@
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713606</t>
+          <t>2026-07-23 16:51:17.420733</t>
         </is>
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713607</t>
-        </is>
+          <t>2026-07-23 16:51:17.420734</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:45:00</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:45:00</t>
+        </is>
+      </c>
+      <c r="AB196" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -21110,13 +23268,26 @@
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713611</t>
+          <t>2026-07-23 16:51:17.420739</t>
         </is>
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713612</t>
-        </is>
+          <t>2026-07-23 16:51:17.420740</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:45:00</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:50:00</t>
+        </is>
+      </c>
+      <c r="AB197" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="198">
@@ -21217,13 +23388,22 @@
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713616</t>
+          <t>2026-07-23 16:51:17.420745</t>
         </is>
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713616</t>
-        </is>
+          <t>2026-07-23 16:51:17.420745</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>2026-04-17 18:55:00</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr"/>
+      <c r="AB198" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -21324,13 +23504,22 @@
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713621</t>
+          <t>2026-07-23 16:51:17.420750</t>
         </is>
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713621</t>
-        </is>
+          <t>2026-07-23 16:51:17.420751</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>2026-04-17 18:55:00</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr"/>
+      <c r="AB199" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -21423,13 +23612,26 @@
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713626</t>
+          <t>2026-07-23 16:51:17.420756</t>
         </is>
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713626</t>
-        </is>
+          <t>2026-07-23 16:51:17.420757</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>2026-04-17 18:55:00</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2026-04-17 18:55:00</t>
+        </is>
+      </c>
+      <c r="AB200" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -21522,13 +23724,26 @@
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713631</t>
+          <t>2026-07-23 16:51:17.420761</t>
         </is>
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713631</t>
-        </is>
+          <t>2026-07-23 16:51:17.420762</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>2026-04-17 18:55:00</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2026-04-17 18:55:00</t>
+        </is>
+      </c>
+      <c r="AB201" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -21629,13 +23844,22 @@
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713636</t>
+          <t>2026-07-23 16:51:17.420767</t>
         </is>
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713637</t>
-        </is>
+          <t>2026-07-23 16:51:17.420768</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:00:00</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr"/>
+      <c r="AB202" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -21736,13 +23960,22 @@
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713641</t>
+          <t>2026-07-23 16:51:17.420773</t>
         </is>
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713642</t>
-        </is>
+          <t>2026-07-23 16:51:17.420774</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:00:00</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr"/>
+      <c r="AB203" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -21835,13 +24068,26 @@
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713646</t>
+          <t>2026-07-23 16:51:17.420778</t>
         </is>
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713647</t>
-        </is>
+          <t>2026-07-23 16:51:17.420779</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:00:00</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:00:00</t>
+        </is>
+      </c>
+      <c r="AB204" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -21934,13 +24180,26 @@
       </c>
       <c r="X205" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713651</t>
+          <t>2026-07-23 16:51:17.420784</t>
         </is>
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713652</t>
-        </is>
+          <t>2026-07-23 16:51:17.420784</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:00:00</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:00:00</t>
+        </is>
+      </c>
+      <c r="AB205" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -22041,13 +24300,22 @@
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713656</t>
+          <t>2026-07-23 16:51:17.420789</t>
         </is>
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713657</t>
-        </is>
+          <t>2026-07-23 16:51:17.420790</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>2026-04-17 23:05:00</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr"/>
+      <c r="AB206" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -22148,13 +24416,22 @@
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713661</t>
+          <t>2026-07-23 16:51:17.420794</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713662</t>
-        </is>
+          <t>2026-07-23 16:51:17.420795</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>2026-04-17 23:05:00</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr"/>
+      <c r="AB207" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -22247,13 +24524,26 @@
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713666</t>
+          <t>2026-07-23 16:51:17.420800</t>
         </is>
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713667</t>
-        </is>
+          <t>2026-07-23 16:51:17.420801</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>2026-04-17 23:05:00</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>2026-04-17 23:05:00</t>
+        </is>
+      </c>
+      <c r="AB208" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -22346,13 +24636,26 @@
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713671</t>
+          <t>2026-07-23 16:51:17.420805</t>
         </is>
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713672</t>
-        </is>
+          <t>2026-07-23 16:51:17.420806</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>2026-04-17 23:05:00</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>2026-04-17 23:05:00</t>
+        </is>
+      </c>
+      <c r="AB209" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -22453,13 +24756,22 @@
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713677</t>
+          <t>2026-07-23 16:51:17.420811</t>
         </is>
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713678</t>
-        </is>
+          <t>2026-07-23 16:51:17.420811</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>2026-04-18 01:10:00</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr"/>
+      <c r="AB210" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -22560,13 +24872,22 @@
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713682</t>
+          <t>2026-07-23 16:51:17.420816</t>
         </is>
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713683</t>
-        </is>
+          <t>2026-07-23 16:51:17.420817</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>2026-04-18 01:10:00</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr"/>
+      <c r="AB211" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -22659,13 +24980,26 @@
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713687</t>
+          <t>2026-07-23 16:51:17.420821</t>
         </is>
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713688</t>
-        </is>
+          <t>2026-07-23 16:51:17.420822</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>2026-04-18 01:10:00</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>2026-04-18 01:10:00</t>
+        </is>
+      </c>
+      <c r="AB212" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -22758,13 +25092,26 @@
       </c>
       <c r="X213" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713692</t>
+          <t>2026-07-23 16:51:17.420827</t>
         </is>
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713693</t>
-        </is>
+          <t>2026-07-23 16:51:17.420828</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>2026-04-18 01:10:00</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>2026-04-18 01:10:00</t>
+        </is>
+      </c>
+      <c r="AB213" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -22865,13 +25212,22 @@
       </c>
       <c r="X214" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713697</t>
+          <t>2026-07-23 16:51:17.420832</t>
         </is>
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713698</t>
-        </is>
+          <t>2026-07-23 16:51:17.420833</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>2026-04-18 03:15:00</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr"/>
+      <c r="AB214" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -22972,13 +25328,22 @@
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713702</t>
+          <t>2026-07-23 16:51:17.420838</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713703</t>
-        </is>
+          <t>2026-07-23 16:51:17.420839</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>2026-04-18 03:15:00</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr"/>
+      <c r="AB215" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -23071,13 +25436,26 @@
       </c>
       <c r="X216" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713707</t>
+          <t>2026-07-23 16:51:17.420844</t>
         </is>
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713708</t>
-        </is>
+          <t>2026-07-23 16:51:17.420844</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>2026-04-18 03:15:00</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>2026-04-18 03:15:00</t>
+        </is>
+      </c>
+      <c r="AB216" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -23170,13 +25548,26 @@
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713712</t>
+          <t>2026-07-23 16:51:17.420849</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713713</t>
-        </is>
+          <t>2026-07-23 16:51:17.420850</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>2026-04-18 03:15:00</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>2026-04-18 03:15:00</t>
+        </is>
+      </c>
+      <c r="AB217" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -23277,13 +25668,22 @@
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713717</t>
+          <t>2026-07-23 16:51:17.420854</t>
         </is>
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713718</t>
-        </is>
+          <t>2026-07-23 16:51:17.420855</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:20:00</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr"/>
+      <c r="AB218" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -23384,13 +25784,22 @@
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713723</t>
+          <t>2026-07-23 16:51:17.420860</t>
         </is>
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713723</t>
-        </is>
+          <t>2026-07-23 16:51:17.420860</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:20:00</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr"/>
+      <c r="AB219" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -23483,13 +25892,26 @@
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713728</t>
+          <t>2026-07-23 16:51:17.420865</t>
         </is>
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713728</t>
-        </is>
+          <t>2026-07-23 16:51:17.420866</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:20:00</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:20:00</t>
+        </is>
+      </c>
+      <c r="AB220" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -23582,13 +26004,26 @@
       </c>
       <c r="X221" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713733</t>
+          <t>2026-07-23 16:51:17.420871</t>
         </is>
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713733</t>
-        </is>
+          <t>2026-07-23 16:51:17.420871</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:20:00</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>2026-04-18 05:20:00</t>
+        </is>
+      </c>
+      <c r="AB221" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -23689,13 +26124,22 @@
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713738</t>
+          <t>2026-07-23 16:51:17.420876</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713738</t>
-        </is>
+          <t>2026-07-23 16:51:17.420877</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:25:00</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr"/>
+      <c r="AB222" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -23796,13 +26240,22 @@
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713743</t>
+          <t>2026-07-23 16:51:17.420881</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713743</t>
-        </is>
+          <t>2026-07-23 16:51:17.420882</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:25:00</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr"/>
+      <c r="AB223" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -23895,13 +26348,26 @@
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713747</t>
+          <t>2026-07-23 16:51:17.420887</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713748</t>
-        </is>
+          <t>2026-07-23 16:51:17.420887</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:25:00</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:25:00</t>
+        </is>
+      </c>
+      <c r="AB224" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -23994,13 +26460,26 @@
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713752</t>
+          <t>2026-07-23 16:51:17.420892</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2026-07-21 21:08:37.713753</t>
-        </is>
+          <t>2026-07-23 16:51:17.420893</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:25:00</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:25:00</t>
+        </is>
+      </c>
+      <c r="AB225" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -24577,7 +27056,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -24721,7 +27200,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -24865,7 +27344,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -25009,7 +27488,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -26305,7 +28784,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -26449,7 +28928,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -26593,7 +29072,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -26737,7 +29216,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -28033,7 +30512,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -28177,7 +30656,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -28321,7 +30800,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -28465,7 +30944,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -29761,7 +32240,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -29905,7 +32384,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -30049,7 +32528,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -30193,7 +32672,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -31489,7 +33968,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -31633,7 +34112,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -31777,7 +34256,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -31921,7 +34400,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -33217,7 +35696,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -33361,7 +35840,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -33505,7 +35984,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -33649,7 +36128,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -34945,7 +37424,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -35089,7 +37568,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -35233,7 +37712,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -35377,7 +37856,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -36673,7 +39152,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -36817,7 +39296,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -36961,7 +39440,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -37105,7 +39584,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -38401,7 +40880,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -39265,7 +41744,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -40129,7 +42608,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -40993,7 +43472,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -41857,7 +44336,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -42721,7 +45200,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -43585,7 +46064,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -44449,7 +46928,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -45169,7 +47648,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -45313,7 +47792,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -46177,7 +48656,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -47041,7 +49520,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -47905,7 +50384,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -48769,7 +51248,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -49633,7 +52112,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -50497,7 +52976,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -51361,7 +53840,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -52081,7 +54560,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
